--- a/artfynd/A 62278-2025 artfynd.xlsx
+++ b/artfynd/A 62278-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62000330</v>
+        <v>95767136</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88965</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>359</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rökfingersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Clavaria fumosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pers.:Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ambricka, Upl</t>
+          <t>291, Älvkarleby, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633421.1354122313</v>
+        <v>633436</v>
       </c>
       <c r="R2" t="n">
-        <v>6710772.846444641</v>
+        <v>6710652</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,27 +751,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-04-26</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-04-26</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>5 blommor</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,68 +775,73 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>67976019</v>
+        <v>62000330</v>
       </c>
       <c r="B3" t="n">
-        <v>98536</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1853</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ambricka, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633423.8554213801</v>
+        <v>633421</v>
       </c>
       <c r="R3" t="n">
-        <v>6710766.045568539</v>
+        <v>6710773</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,31 +868,21 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-06-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-06-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>eftersökt ej funnen, koordinat bör vara felaktig!</t>
+          <t>5 blommor</t>
         </is>
       </c>
       <c r="AD3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
@@ -918,61 +905,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95767136</v>
+        <v>92765390</v>
       </c>
       <c r="B4" t="n">
-        <v>84986</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>359</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rökfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Clavaria fumosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pers.:Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>291, Älvkarleby, Upl</t>
+          <t>Ambricka, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633435.9638940437</v>
+        <v>633422</v>
       </c>
       <c r="R4" t="n">
-        <v>6710652.125709963</v>
+        <v>6710773</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,24 +977,24 @@
           <t>Älvkarleby</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>C-Älv-0458</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:48</t>
+          <t>2016-04-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:48</t>
+          <t>2016-04-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>5 blommor, 30 plantor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,29 +1003,32 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>124971610</v>
       </c>
       <c r="B5" t="n">
-        <v>98269</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,6 +1138,214 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>96940257</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99754</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222295</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vårstarr</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carex caryophyllea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ambricka, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>633174</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6710639</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-05-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-05-20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>81678843</v>
+      </c>
+      <c r="B7" t="n">
+        <v>103695</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>224412</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Hårig sandviol</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Viola rupestris var. rupestris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ambricka, KLG, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>633176</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6710636</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2019-05-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2019-05-11</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62278-2025 artfynd.xlsx
+++ b/artfynd/A 62278-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95767136</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62000330</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1022,6 +1037,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92765390</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1138,6 +1158,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124971610</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1244,6 +1269,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96940257</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1346,8 +1376,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81678843</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>